--- a/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
@@ -3180,38 +3180,30 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>42942000</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>34000</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K42" s="5" t="n">
+        <v>42942000</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>34000</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3220,7 +3212,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -40708,7 +40700,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -40718,7 +40710,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -41116,12 +41108,12 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 1263呎 (4+房)
-招标单位
--
-(在售)</t>
+$4294万
+$34,000/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
@@ -3185,7 +3185,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -4110,38 +4110,30 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>39530400</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>31200</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K57" s="5" t="n">
+        <v>39530400</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>31200</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4150,7 +4142,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -40700,7 +40692,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -40710,7 +40702,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -41113,7 +41105,7 @@
           <t>A | 1263呎 (4+房)
 $4294万
 $34,000/呎
-(26年-09月-21日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -41272,12 +41264,12 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 1267呎 (4+房)
-招标单位
--
-(在售)</t>
+$3953万
+$31,200/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>38038000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>30093</v>
+        <v>30117</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>38038000</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>30093</v>
+        <v>30117</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
@@ -41344,9 +41344,9 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>A | 1264呎 (4+房)
+          <t>A | 1263呎 (4+房)
 $3804万
-$30,093/呎
+$30,117/呎
 (24年-04月-29日)</t>
         </is>
       </c>
